--- a/자료/롯데패키징 미등록상품 29건.xlsx
+++ b/자료/롯데패키징 미등록상품 29건.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="100">
   <si>
     <t>번호</t>
   </si>
@@ -305,6 +305,54 @@
   </si>
   <si>
     <t>LT/다기능분사기(SC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT/미니니퍼115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT/샤워플러스 녹물제거 필터샤워기(온오프기능)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT/샤워플러스 샤워기 리필필터 4P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT/샤워플러스 샤워기 염소볼 1P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HB/몬스툴가스토치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TSP/가스점화라이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT/주방용회전형절수기레이저헤드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품확인 안됨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>규격정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롯데알미늄 전산 등록 코드 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미확인 상품 정보 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자재명 롯데전산에서 재확인</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -331,12 +379,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -351,9 +405,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -693,14 +749,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.77734375" customWidth="1"/>
     <col min="2" max="2" width="40.77734375" customWidth="1"/>
     <col min="3" max="3" width="18.77734375" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.21875" customWidth="1"/>
+    <col min="5" max="5" width="43.21875" customWidth="1"/>
     <col min="6" max="8" width="18.77734375" customWidth="1"/>
     <col min="9" max="9" width="10.77734375" customWidth="1"/>
     <col min="10" max="10" width="40.77734375" customWidth="1"/>
@@ -1222,6 +1278,12 @@
       <c r="C23" t="s">
         <v>49</v>
       </c>
+      <c r="D23" s="1">
+        <v>8801235242881</v>
+      </c>
+      <c r="E23" t="s">
+        <v>88</v>
+      </c>
       <c r="I23">
         <v>1905</v>
       </c>
@@ -1229,20 +1291,24 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="24" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I24">
+      <c r="D24" s="3"/>
+      <c r="E24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="2">
         <v>1798</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1256,6 +1322,12 @@
       <c r="C25" t="s">
         <v>53</v>
       </c>
+      <c r="D25" s="1">
+        <v>8809591492223</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
+      </c>
       <c r="I25">
         <v>0</v>
       </c>
@@ -1273,6 +1345,12 @@
       <c r="C26" t="s">
         <v>55</v>
       </c>
+      <c r="D26" s="1">
+        <v>8809591491783</v>
+      </c>
+      <c r="E26" t="s">
+        <v>90</v>
+      </c>
       <c r="I26">
         <v>0</v>
       </c>
@@ -1290,6 +1368,12 @@
       <c r="C27" t="s">
         <v>57</v>
       </c>
+      <c r="D27" s="1">
+        <v>8809591491691</v>
+      </c>
+      <c r="E27" t="s">
+        <v>91</v>
+      </c>
       <c r="I27">
         <v>0</v>
       </c>
@@ -1307,6 +1391,12 @@
       <c r="C28" t="s">
         <v>59</v>
       </c>
+      <c r="D28" s="1">
+        <v>8809057638769</v>
+      </c>
+      <c r="E28" t="s">
+        <v>92</v>
+      </c>
       <c r="I28">
         <v>0</v>
       </c>
@@ -1324,6 +1414,12 @@
       <c r="C29" t="s">
         <v>61</v>
       </c>
+      <c r="D29" s="1">
+        <v>8809148124034</v>
+      </c>
+      <c r="E29" t="s">
+        <v>93</v>
+      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -1341,11 +1437,37 @@
       <c r="C30" t="s">
         <v>63</v>
       </c>
+      <c r="D30" s="1">
+        <v>8801235244274</v>
+      </c>
+      <c r="E30" t="s">
+        <v>94</v>
+      </c>
       <c r="I30">
         <v>540</v>
       </c>
       <c r="J30" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
